--- a/output2/【河洛話注音】上有力量的每日祈禱文.xlsx
+++ b/output2/【河洛話注音】上有力量的每日祈禱文.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\output2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149A57A4-A2B0-4AC8-9CE5-ACD17F79FEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33CEC4A-A578-453B-8615-A43815D95A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22020" yWindow="2235" windowWidth="17280" windowHeight="12870" xr2:uid="{E23BB67B-2398-4558-8CA4-C220D0D18289}"/>
-    <workbookView xWindow="-21675" yWindow="2580" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="11" xr2:uid="{C27737B3-5DFE-41F8-BAC0-DD5E8D289269}"/>
+    <workbookView xWindow="-21675" yWindow="2580" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="7" xr2:uid="{C27737B3-5DFE-41F8-BAC0-DD5E8D289269}"/>
   </bookViews>
   <sheets>
     <sheet name="雙排注音" sheetId="12" r:id="rId1"/>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -4057,7 +4057,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -4796,7 +4796,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -5535,7 +5535,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -6274,7 +6274,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -7013,7 +7013,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -7752,7 +7752,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -9699,20 +9699,20 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>45</v>
+        <v>609</v>
       </c>
       <c r="B95" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C95:E95)</f>
-        <v>Øu2</v>
+        <v>hoo7</v>
       </c>
       <c r="C95" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="D95" t="s">
-        <v>139</v>
+        <v>194</v>
       </c>
       <c r="E95">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F95">
         <v>2</v>

--- a/output2/【河洛話注音】上有力量的每日祈禱文.xlsx
+++ b/output2/【河洛話注音】上有力量的每日祈禱文.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\output2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33CEC4A-A578-453B-8615-A43815D95A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1415AD25-3EB6-4E07-8595-DA9257D7CBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22020" yWindow="2235" windowWidth="17280" windowHeight="12870" xr2:uid="{E23BB67B-2398-4558-8CA4-C220D0D18289}"/>
-    <workbookView xWindow="-21675" yWindow="2580" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="7" xr2:uid="{C27737B3-5DFE-41F8-BAC0-DD5E8D289269}"/>
+    <workbookView xWindow="5820" yWindow="2475" windowWidth="17280" windowHeight="12870" xr2:uid="{E23BB67B-2398-4558-8CA4-C220D0D18289}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="7" xr2:uid="{C27737B3-5DFE-41F8-BAC0-DD5E8D289269}"/>
   </bookViews>
   <sheets>
     <sheet name="雙排注音" sheetId="12" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="684">
   <si>
     <t>Key</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -516,9 +516,6 @@
     <t>hian5</t>
   </si>
   <si>
-    <t>ian</t>
-  </si>
-  <si>
     <t>ping5</t>
   </si>
   <si>
@@ -788,9 +785,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;和&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;高五喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;堅五喜&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;靈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;經五柳&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -987,9 +981,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;和&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄜˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄏㄧㄢˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;靈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄌㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -1185,9 +1176,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;和&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hô&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hîan&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;靈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;lêng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -1422,9 +1410,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;和&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hó&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hían&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;靈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;líng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -1602,9 +1587,6 @@
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;和&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ho5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;hian5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;靈&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ling5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -1795,9 +1777,6 @@
   </si>
   <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;和&lt;/rb&gt;&lt;rt&gt;ho5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄜˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rt&gt;hian5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㄧㄢˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;靈&lt;/rb&gt;&lt;rt&gt;ling5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
@@ -2224,6 +2203,35 @@
   </si>
   <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;與&lt;/rb&gt;&lt;rt&gt;hoo7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄏㆦ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>p</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;經五邊&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄅㄧㄥˊ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pêng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;pîng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;bíng&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ping5&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;平&lt;/rb&gt;&lt;rt&gt;ping5&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄅㄧㄥˊ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
 </sst>
 </file>
@@ -2678,102 +2686,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2783,12 +2791,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -2798,12 +2806,12 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -2813,47 +2821,47 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -2863,37 +2871,37 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -2903,32 +2911,32 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -2938,32 +2946,32 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -2973,57 +2981,57 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>573</v>
+        <v>683</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -3033,22 +3041,22 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -3058,57 +3066,57 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -3118,32 +3126,32 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -3153,27 +3161,27 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="101" spans="1:1">
@@ -3183,72 +3191,72 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
     </row>
     <row r="116" spans="1:1">
@@ -3258,17 +3266,17 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -3278,27 +3286,27 @@
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -3308,37 +3316,37 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -3348,42 +3356,42 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -3393,12 +3401,12 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3483,22 +3491,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -3550,7 +3558,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -3577,102 +3585,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3682,12 +3690,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -3697,12 +3705,12 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -3712,47 +3720,47 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -3762,37 +3770,37 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -3802,32 +3810,32 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -3837,32 +3845,32 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -3872,57 +3880,57 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>508</v>
+        <v>682</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -3932,22 +3940,22 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -3957,57 +3965,57 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -4017,32 +4025,32 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -4052,27 +4060,27 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="101" spans="1:1">
@@ -4082,72 +4090,72 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="116" spans="1:1">
@@ -4157,17 +4165,17 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -4177,27 +4185,27 @@
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -4207,37 +4215,37 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -4247,42 +4255,42 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -4292,12 +4300,12 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4316,102 +4324,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -4421,12 +4429,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -4436,12 +4444,12 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -4451,47 +4459,47 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -4501,37 +4509,37 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -4541,32 +4549,32 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -4576,32 +4584,32 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -4611,57 +4619,57 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>448</v>
+        <v>681</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -4671,22 +4679,22 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -4696,57 +4704,57 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -4756,32 +4764,32 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -4791,27 +4799,27 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="101" spans="1:1">
@@ -4821,72 +4829,72 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="116" spans="1:1">
@@ -4896,17 +4904,17 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -4916,27 +4924,27 @@
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -4946,37 +4954,37 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -4986,42 +4994,42 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -5031,12 +5039,12 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5055,102 +5063,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -5160,12 +5168,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -5175,12 +5183,12 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -5190,47 +5198,47 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -5240,37 +5248,37 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -5280,32 +5288,32 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -5315,32 +5323,32 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -5350,57 +5358,57 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>369</v>
+        <v>680</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -5410,22 +5418,22 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -5435,57 +5443,57 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -5495,32 +5503,32 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -5530,27 +5538,27 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="101" spans="1:1">
@@ -5560,72 +5568,72 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="116" spans="1:1">
@@ -5635,17 +5643,17 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -5655,27 +5663,27 @@
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -5685,37 +5693,37 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -5725,42 +5733,42 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -5770,12 +5778,12 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5794,102 +5802,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -5899,12 +5907,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -5914,12 +5922,12 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -5929,47 +5937,47 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -5979,37 +5987,37 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -6019,32 +6027,32 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -6054,32 +6062,32 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -6089,57 +6097,57 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>369</v>
+        <v>679</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -6149,22 +6157,22 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -6174,57 +6182,57 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -6234,32 +6242,32 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -6269,27 +6277,27 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="101" spans="1:1">
@@ -6299,72 +6307,72 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="116" spans="1:1">
@@ -6374,17 +6382,17 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -6394,27 +6402,27 @@
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -6424,37 +6432,37 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -6464,42 +6472,42 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -6509,12 +6517,12 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -6533,102 +6541,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -6638,12 +6646,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6653,12 +6661,12 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -6668,47 +6676,47 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -6718,37 +6726,37 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -6758,32 +6766,32 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -6793,32 +6801,32 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -6828,57 +6836,57 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>303</v>
+        <v>678</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -6888,22 +6896,22 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -6913,57 +6921,57 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -6973,32 +6981,32 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -7008,27 +7016,27 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="101" spans="1:1">
@@ -7038,72 +7046,72 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="116" spans="1:1">
@@ -7113,17 +7121,17 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -7133,27 +7141,27 @@
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -7163,37 +7171,37 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -7203,42 +7211,42 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -7248,12 +7256,12 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -7272,102 +7280,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -7377,12 +7385,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -7392,12 +7400,12 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -7407,47 +7415,47 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -7457,37 +7465,37 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -7497,32 +7505,32 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -7532,32 +7540,32 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -7567,57 +7575,57 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>237</v>
+        <v>677</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -7627,22 +7635,22 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -7652,57 +7660,57 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -7712,32 +7720,32 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -7747,27 +7755,27 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101" spans="1:1">
@@ -7777,72 +7785,72 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="116" spans="1:1">
@@ -7852,17 +7860,17 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -7872,27 +7880,27 @@
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -7902,37 +7910,37 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -7942,42 +7950,42 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -7987,12 +7995,12 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -8008,17 +8016,17 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="B1" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C1:E1)</f>
         <v>siong7</v>
       </c>
       <c r="C1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" t="s">
         <v>189</v>
-      </c>
-      <c r="D1" t="s">
-        <v>190</v>
       </c>
       <c r="E1">
         <v>7</v>
@@ -8039,7 +8047,7 @@
         <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -8101,7 +8109,7 @@
         <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -8119,10 +8127,10 @@
         <v>mui5</v>
       </c>
       <c r="C6" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="D6" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -8233,7 +8241,7 @@
         <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -8294,7 +8302,7 @@
         <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -8357,10 +8365,10 @@
         <v>can2</v>
       </c>
       <c r="C20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" t="s">
         <v>184</v>
-      </c>
-      <c r="D20" t="s">
-        <v>185</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -8448,7 +8456,7 @@
         <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -8486,10 +8494,10 @@
         <v>ka2</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -8570,7 +8578,7 @@
         <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -8716,7 +8724,7 @@
         <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E40">
         <v>5</v>
@@ -8772,17 +8780,17 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="B44" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C44:E44)</f>
         <v>siong7</v>
       </c>
       <c r="C44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" t="s">
         <v>189</v>
-      </c>
-      <c r="D44" t="s">
-        <v>190</v>
       </c>
       <c r="E44">
         <v>7</v>
@@ -8843,7 +8851,7 @@
         <v>84</v>
       </c>
       <c r="D47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E47">
         <v>5</v>
@@ -9087,14 +9095,15 @@
       <c r="A61" t="s">
         <v>50</v>
       </c>
-      <c r="B61" t="s">
-        <v>151</v>
+      <c r="B61" s="5" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(C61:E61)</f>
+        <v>ping5</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>675</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
+        <v>676</v>
       </c>
       <c r="E61">
         <v>5</v>
@@ -9112,10 +9121,10 @@
         <v>ka2</v>
       </c>
       <c r="C62" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -9136,7 +9145,7 @@
         <v>106</v>
       </c>
       <c r="D63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -9170,7 +9179,7 @@
         <v>52</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C65" t="s">
         <v>121</v>
@@ -9197,7 +9206,7 @@
         <v>84</v>
       </c>
       <c r="D66" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E66">
         <v>5</v>
@@ -9215,7 +9224,7 @@
         <v>kai3</v>
       </c>
       <c r="C67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D67" t="s">
         <v>127</v>
@@ -9232,13 +9241,13 @@
         <v>54</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
         <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E68">
         <v>8</v>
@@ -9269,7 +9278,7 @@
         <v>106</v>
       </c>
       <c r="D71" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E71">
         <v>2</v>
@@ -9345,17 +9354,17 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B76" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C76:E76)</f>
         <v>kap4</v>
       </c>
       <c r="C76" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D76" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E76">
         <v>4</v>
@@ -9373,10 +9382,10 @@
         <v>can2</v>
       </c>
       <c r="C77" t="s">
+        <v>183</v>
+      </c>
+      <c r="D77" t="s">
         <v>184</v>
-      </c>
-      <c r="D77" t="s">
-        <v>185</v>
       </c>
       <c r="E77">
         <v>2</v>
@@ -9447,7 +9456,7 @@
         <v>57</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C81" t="s">
         <v>84</v>
@@ -9467,7 +9476,7 @@
         <v>58</v>
       </c>
       <c r="B82" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C82" t="s">
         <v>84</v>
@@ -9494,7 +9503,7 @@
         <v>84</v>
       </c>
       <c r="D83" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -9512,10 +9521,10 @@
         <v>kiann2</v>
       </c>
       <c r="C84" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D84" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E84">
         <v>2</v>
@@ -9529,7 +9538,7 @@
         <v>60</v>
       </c>
       <c r="B85" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C85" t="s">
         <v>96</v>
@@ -9551,7 +9560,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B87" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C87:E87)</f>
@@ -9561,7 +9570,7 @@
         <v>84</v>
       </c>
       <c r="D87" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -9575,7 +9584,7 @@
         <v>61</v>
       </c>
       <c r="B88" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s">
         <v>119</v>
@@ -9595,7 +9604,7 @@
         <v>62</v>
       </c>
       <c r="B89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C89" t="s">
         <v>124</v>
@@ -9615,7 +9624,7 @@
         <v>63</v>
       </c>
       <c r="B90" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C90" t="s">
         <v>99</v>
@@ -9635,7 +9644,7 @@
         <v>64</v>
       </c>
       <c r="B91" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C91" t="s">
         <v>92</v>
@@ -9662,7 +9671,7 @@
         <v>119</v>
       </c>
       <c r="D92" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -9685,7 +9694,7 @@
         <v>su3</v>
       </c>
       <c r="C94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D94" t="s">
         <v>139</v>
@@ -9699,17 +9708,17 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B95" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C95:E95)</f>
         <v>hoo7</v>
       </c>
       <c r="C95" t="s">
+        <v>192</v>
+      </c>
+      <c r="D95" t="s">
         <v>193</v>
-      </c>
-      <c r="D95" t="s">
-        <v>194</v>
       </c>
       <c r="E95">
         <v>7</v>
@@ -9730,7 +9739,7 @@
         <v>106</v>
       </c>
       <c r="D96" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E96">
         <v>2</v>
@@ -9744,7 +9753,7 @@
         <v>66</v>
       </c>
       <c r="B97" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C97" t="s">
         <v>99</v>
@@ -9764,7 +9773,7 @@
         <v>67</v>
       </c>
       <c r="B98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C98" t="s">
         <v>119</v>
@@ -9801,7 +9810,7 @@
         <v>106</v>
       </c>
       <c r="D101" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E101">
         <v>2</v>
@@ -9815,7 +9824,7 @@
         <v>68</v>
       </c>
       <c r="B102" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C102" t="s">
         <v>124</v>
@@ -9859,10 +9868,10 @@
         <v>soo2</v>
       </c>
       <c r="C104" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D104" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E104">
         <v>2</v>
@@ -9883,7 +9892,7 @@
         <v>84</v>
       </c>
       <c r="D105" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E105">
         <v>7</v>
@@ -9897,7 +9906,7 @@
         <v>71</v>
       </c>
       <c r="B106" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C106" t="s">
         <v>119</v>
@@ -9917,13 +9926,13 @@
         <v>72</v>
       </c>
       <c r="B107" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C107" t="s">
         <v>96</v>
       </c>
       <c r="D107" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E107">
         <v>5</v>
@@ -9941,10 +9950,10 @@
         <v>kap4</v>
       </c>
       <c r="C108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D108" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E108">
         <v>4</v>
@@ -9958,7 +9967,7 @@
         <v>71</v>
       </c>
       <c r="B109" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C109" t="s">
         <v>119</v>
@@ -9978,13 +9987,13 @@
         <v>73</v>
       </c>
       <c r="B110" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C110" t="s">
         <v>82</v>
       </c>
       <c r="D110" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E110">
         <v>4</v>
@@ -10005,7 +10014,7 @@
         <v>84</v>
       </c>
       <c r="D111" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E111">
         <v>5</v>
@@ -10026,7 +10035,7 @@
         <v>99</v>
       </c>
       <c r="D112" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E112">
         <v>3</v>
@@ -10040,7 +10049,7 @@
         <v>75</v>
       </c>
       <c r="B113" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C113" t="s">
         <v>121</v>
@@ -10072,7 +10081,7 @@
         <v>106</v>
       </c>
       <c r="D115" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E115">
         <v>2</v>
@@ -10148,17 +10157,17 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B120" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C120:E120)</f>
         <v>kap4</v>
       </c>
       <c r="C120" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D120" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E120">
         <v>4</v>
@@ -10176,10 +10185,10 @@
         <v>can2</v>
       </c>
       <c r="C121" t="s">
+        <v>183</v>
+      </c>
+      <c r="D121" t="s">
         <v>184</v>
-      </c>
-      <c r="D121" t="s">
-        <v>185</v>
       </c>
       <c r="E121">
         <v>2</v>
@@ -10207,7 +10216,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B123" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C123:E123)</f>
@@ -10217,7 +10226,7 @@
         <v>84</v>
       </c>
       <c r="D123" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -10230,7 +10239,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B125" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C125:E125)</f>
@@ -10240,7 +10249,7 @@
         <v>84</v>
       </c>
       <c r="D125" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E125">
         <v>1</v>
@@ -10251,7 +10260,7 @@
         <v>61</v>
       </c>
       <c r="B126" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C126" t="s">
         <v>119</v>
@@ -10318,7 +10327,7 @@
         <v>84</v>
       </c>
       <c r="D129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E129">
         <v>5</v>
@@ -10352,13 +10361,13 @@
         <v>78</v>
       </c>
       <c r="B131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C131" t="s">
         <v>112</v>
       </c>
       <c r="D131" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E131">
         <v>2</v>
@@ -10384,7 +10393,7 @@
         <v>119</v>
       </c>
       <c r="D133" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E133">
         <v>3</v>
@@ -10395,17 +10404,17 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B134" s="5" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(C134:E134)</f>
         <v>hoo7</v>
       </c>
       <c r="C134" t="s">
+        <v>192</v>
+      </c>
+      <c r="D134" t="s">
         <v>193</v>
-      </c>
-      <c r="D134" t="s">
-        <v>194</v>
       </c>
       <c r="E134">
         <v>7</v>
@@ -10426,7 +10435,7 @@
         <v>106</v>
       </c>
       <c r="D135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E135">
         <v>2</v>
@@ -10460,7 +10469,7 @@
         <v>79</v>
       </c>
       <c r="B137" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C137" t="s">
         <v>119</v>
@@ -10487,7 +10496,7 @@
         <v>84</v>
       </c>
       <c r="D138" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E138">
         <v>5</v>
@@ -10505,10 +10514,10 @@
         <v>theh8</v>
       </c>
       <c r="C139" t="s">
+        <v>196</v>
+      </c>
+      <c r="D139" t="s">
         <v>197</v>
-      </c>
-      <c r="D139" t="s">
-        <v>198</v>
       </c>
       <c r="E139">
         <v>8</v>
@@ -10522,7 +10531,7 @@
         <v>81</v>
       </c>
       <c r="B140" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C140" t="s">
         <v>119</v>
@@ -11181,7 +11190,7 @@
         <v>50</v>
       </c>
       <c r="D37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -11266,7 +11275,7 @@
         <v>53</v>
       </c>
       <c r="D42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -11283,7 +11292,7 @@
         <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -11317,7 +11326,7 @@
         <v>53</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -11334,7 +11343,7 @@
         <v>54</v>
       </c>
       <c r="D46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -11351,7 +11360,7 @@
         <v>54</v>
       </c>
       <c r="D47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -11436,7 +11445,7 @@
         <v>56</v>
       </c>
       <c r="D52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -11487,7 +11496,7 @@
         <v>57</v>
       </c>
       <c r="D55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -11504,7 +11513,7 @@
         <v>57</v>
       </c>
       <c r="D56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -11521,7 +11530,7 @@
         <v>60</v>
       </c>
       <c r="D57" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -11538,7 +11547,7 @@
         <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -11759,7 +11768,7 @@
         <v>56</v>
       </c>
       <c r="D71" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -11878,7 +11887,7 @@
         <v>80</v>
       </c>
       <c r="D78" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -11895,7 +11904,7 @@
         <v>80</v>
       </c>
       <c r="D79" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E79">
         <v>0</v>
